--- a/docs/EchoMind_Audit_2026-10-14_Project2/03_Communication_with_Client/EM26-27_Client_Communication_Log.xlsx
+++ b/docs/EchoMind_Audit_2026-10-14_Project2/03_Communication_with_Client/EM26-27_Client_Communication_Log.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Document control" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Communication log'!$A$4:$G$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Communication log'!$A$4:$I$24</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Document control'!$A$4:$B$15</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -462,16 +462,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:I24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="70" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
+    <col width="50" customWidth="1" min="5" max="5"/>
     <col width="40" customWidth="1" min="6" max="6"/>
-    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="34" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="48" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -484,7 +486,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>EM26-27 Client communication log — issued 2026-10-13. Dates from the 2025 plan, Jira and SOW, and from the 2026 client reviews (EM26-19).</t>
+          <t>EM26-27 Client communication log, rev 1.1 — 2026-10-14. Every client meeting is recorded as a review in EM26-19 (or as a contract in EM26-28); the last column says where.</t>
         </is>
       </c>
     </row>
@@ -501,27 +503,37 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Direction</t>
+          <t>Type</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>Subject / outcome</t>
+          <t>Subject</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Channel</t>
+          <t>Feedback / discussion</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>Record</t>
+          <t>Outcome / decision</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>Year</t>
+          <t>Requirements (FR / NFR)</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>Actions</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>Meeting recorded in</t>
         </is>
       </c>
     </row>
@@ -538,27 +550,37 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>AJACE → client</t>
+          <t>E-mail</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>Product documentation, specification and sizing sent</t>
+          <t>Product specification, sizing and capacity</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>E-mail</t>
+          <t>Customer requested specification before contract</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>SDLC plan P1–P3 (‘done as per email’)</t>
+          <t>Requirements clarified</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>FR-2025-01 … 04</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>2025 SDLC plan P1–P3</t>
         </is>
       </c>
     </row>
@@ -575,27 +597,37 @@
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>AJACE → client</t>
+          <t>E-mail</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>Contract revised (upfront-payment clause removed, reviewed with Antony Johan) and sent</t>
+          <t>Contract revision</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>E-mail (PDF)</t>
+          <t>Upfront-payment clause not acceptable to the customer</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>SDLC plan C1–C3; signed contract held by AJACE</t>
+          <t>Clause removed; revised contract sent</t>
         </is>
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>EM26-28 CON-2025-01; 2025 SDLC plan C1–C3</t>
         </is>
       </c>
     </row>
@@ -612,27 +644,37 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>AJACE → client</t>
+          <t>E-mail</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>Follow-up on the purchase-order delay (client financial audit); August kick-off confirmed</t>
+          <t>Purchase-order delay</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>E-mail</t>
+          <t>Customer financial audit delayed the PO</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>Jira EMD-02</t>
+          <t>Start confirmed for August</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>2025 Jira EMD-02</t>
         </is>
       </c>
     </row>
@@ -649,27 +691,37 @@
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>Both</t>
+          <t>Contract</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>Statement of work signed by both parties</t>
+          <t>Statement of work</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>DocuSign</t>
+          <t>Scope, price, warranty, consulting, acceptance</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>Project documentation; DR-2025-09</t>
+          <t>SOW signed by both parties</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>FR-2025-01 … 05; NFR-2025-01, -08</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr">
+        <is>
+          <t>EM26-28 CON-2025-01; review record DR-2025-09</t>
         </is>
       </c>
     </row>
@@ -686,27 +738,37 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>AJACE → client</t>
+          <t>E-mail</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>Shipping confirmation and tracking; delivery ETA 2025-09-17</t>
+          <t>Shipping confirmation and tracking</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>E-mail</t>
+          <t>Delivery ETA 2025-09-17</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>Jira EMD-12</t>
+          <t>Appliance shipped</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr">
+        <is>
+          <t>2025 Jira EMD-12</t>
         </is>
       </c>
     </row>
@@ -723,145 +785,185 @@
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>AJACE</t>
+          <t>Review</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>Final release package approved and released</t>
+          <t>Final release package</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>Review</t>
+          <t>Release package and shipment checked</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>DR-1.0 (MM-2025-09-01)</t>
+          <t>Approved and released</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>FR-2025-01 … 05</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>DA-2025-09</t>
+        </is>
+      </c>
+      <c r="I10" s="4" t="inlineStr">
+        <is>
+          <t>EM26-19 review log › DR-2025-13; review record DR-2025-13</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2025-10</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Client A; Client B (Bahrain)</t>
+          <t>2025 university pilot customer</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>Client ↔ AJACE</t>
+          <t>Contract</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>Requirements — Client A; Client B (Bahrain): 3 requirements: personal AI assistant; conversation assistance; DoD FMR financial knowledge base</t>
+          <t>EchoMind White edition</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>Demonstration / meeting</t>
+          <t>Always-listening transcript, knowledge base and chatbot for research and data analysis</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>Review record CR-2026-02; correspondence to be filed</t>
+          <t>Contracted</t>
         </is>
       </c>
       <c r="G11" s="4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>FR-LT-01, FR-KC-01, FR-KC-02</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="inlineStr">
+        <is>
+          <t>EM26-28 CON-2025-02</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2025-12</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>Client A; Client B (Bahrain)</t>
+          <t>Client B (Bahrain)</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>Client ↔ AJACE</t>
+          <t>Contract meeting</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>Conversation assistance v1 (Kyutai Unmute stack): Not natural; too slow</t>
+          <t>Full-duplex conversation assistant</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>Demonstration / meeting</t>
+          <t>Five personas: health care, finance and banking, retail, government and public sector, dealerships</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>Review record CR-2026-03; correspondence to be filed</t>
+          <t>Contract accepted</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>FR-VC-01, FR-KC-05</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I12" s="4" t="inlineStr">
+        <is>
+          <t>EM26-28 CON-2025-03</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Client A; Client B (Bahrain)</t>
+          <t>Internal — management</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>Client ↔ AJACE</t>
+          <t>Meeting</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>Conversation assistance v2 (NVIDIA PersonaPlex): Fast, but cannot use the customer's large knowledge base in spoken conversation</t>
+          <t>Platform for the next generation</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>Demonstration / meeting</t>
+          <t>Portable AI supercomputer available; PC appliance limits capacity</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>Review record CR-2026-04; correspondence to be filed</t>
+          <t>Move to the DGX Spark</t>
         </is>
       </c>
       <c r="G13" s="4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>FR-PL-01; NFR-D01</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>AC-20</t>
+        </is>
+      </c>
+      <c r="I13" s="4" t="inlineStr">
+        <is>
+          <t>EM26-19 review log › CR-2026-01; review record CR-2026-01</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
@@ -871,106 +973,512 @@
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>Client ↔ AJACE</t>
+          <t>Contract meeting</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>Live transcription: Accuracy and speed below need (e.g. 'DoD FMR' heard as 'DODFMA')</t>
+          <t>Government project — performance and private assistant</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>Demonstration / meeting</t>
+          <t>Knowledge chat, live transcript, word cloud, conversation assistant; feedback given on the proposed flow</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>Review record CR-2026-06; correspondence to be filed</t>
+          <t>Contract signed</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>FR-KC-01, FR-KC-02, FR-LT-01, FR-LT-04, FR-VC-01</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I14" s="4" t="inlineStr">
+        <is>
+          <t>EM26-28 CON-2026-01</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Client C (law firm)</t>
+          <t>Client A; Client B (Bahrain)</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>Client ↔ AJACE</t>
+          <t>Requirements meeting</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>Conversation and live transcript demonstration: Needs a listen-only assistant that pulls supporting data onto the screen while people speak</t>
+          <t>Requirements for 2026</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>Demonstration / meeting</t>
+          <t>Personal AI assistant; conversation assistance; financial knowledge base on the DoD FMR</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>Review record CR-2026-07; correspondence to be filed</t>
+          <t>Accepted; three workstreams</t>
         </is>
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>FR-VC-03, FR-KC-05, FR-VC-01, FR-KC-04; NFR-Q01 … Q04</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>AC-21, AC-22</t>
+        </is>
+      </c>
+      <c r="I15" s="4" t="inlineStr">
+        <is>
+          <t>EM26-19 review log › CR-2026-02; review record CR-2026-02</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>Client A; Client B (Bahrain)</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>Demonstration</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>Conversation assistance v1 (Kyutai Unmute)</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>Not natural; too slow</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>Move to NVIDIA PersonaPlex</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="inlineStr">
+        <is>
+          <t>FR-VC-01; NFR-P04, NFR-P07</t>
+        </is>
+      </c>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>AC-23</t>
+        </is>
+      </c>
+      <c r="I16" s="4" t="inlineStr">
+        <is>
+          <t>EM26-19 review log › CR-2026-03; review record CR-2026-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>Client A</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>Conference request</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>Financial assistant on the DoD FMR</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>Assistant needed for a March conference</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>Delivered in March</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="inlineStr">
+        <is>
+          <t>FR-KC-04, FR-KC-05</t>
+        </is>
+      </c>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I17" s="4" t="inlineStr">
+        <is>
+          <t>EM26-28 CON-2026-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>2026-03 → 04</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>Client A; Client B (Bahrain)</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>Demonstration</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>Conversation assistance v2 (PersonaPlex)</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>Fast, but must use the client's large data in spoken conversation</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>Build our own dual-loop conversation flow</t>
+        </is>
+      </c>
+      <c r="G18" s="4" t="inlineStr">
+        <is>
+          <t>FR-VC-01, FR-VC-02; NFR-P04</t>
+        </is>
+      </c>
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t>AC-24</t>
+        </is>
+      </c>
+      <c r="I18" s="4" t="inlineStr">
+        <is>
+          <t>EM26-19 review log › CR-2026-04; review record CR-2026-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>Internal — Project Lead</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>Design review</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>Field deployment</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>How is a unit reached on a site with no network?</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>Boot-time hotspot with a landing page</t>
+        </is>
+      </c>
+      <c r="G19" s="4" t="inlineStr">
+        <is>
+          <t>FR-PL-06</t>
+        </is>
+      </c>
+      <c r="H19" s="4" t="inlineStr">
+        <is>
+          <t>AC-25, AC-26</t>
+        </is>
+      </c>
+      <c r="I19" s="4" t="inlineStr">
+        <is>
+          <t>EM26-19 review log › CR-2026-05; review record CR-2026-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>Client A</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>Feedback</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>Live transcription</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>Accuracy and speed below need (e.g. 'DoD FMR' misheard)</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>Better speech model with fallback; chat moved from Ollama to TensorRT-LLM</t>
+        </is>
+      </c>
+      <c r="G20" s="4" t="inlineStr">
+        <is>
+          <t>FR-LT-01, FR-LT-02; NFR-P01, NFR-P06</t>
+        </is>
+      </c>
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t>AC-27, AC-28, AC-29</t>
+        </is>
+      </c>
+      <c r="I20" s="4" t="inlineStr">
+        <is>
+          <t>EM26-19 review log › CR-2026-06; review record CR-2026-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>Client C (law firm)</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>Demonstration</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>Conversation and live transcript</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>Likes both; wants an assistant that listens, pulls data onto the screen and does not reply</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>Build the Silent Assistant</t>
+        </is>
+      </c>
+      <c r="G21" s="4" t="inlineStr">
+        <is>
+          <t>FR-SA-01, FR-SA-02, FR-SA-03</t>
+        </is>
+      </c>
+      <c r="H21" s="4" t="inlineStr">
+        <is>
+          <t>AC-30, AC-31</t>
+        </is>
+      </c>
+      <c r="I21" s="4" t="inlineStr">
+        <is>
+          <t>EM26-19 review log › CR-2026-07; review record CR-2026-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>Internal — design</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>Design review</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>Group discussions (Boardroom)</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>Speaker separation needed; diarisation models compared by trial</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t>Build Boardroom with VibeVoice-ASR</t>
+        </is>
+      </c>
+      <c r="G22" s="4" t="inlineStr">
+        <is>
+          <t>FR-BR-01, FR-BR-02</t>
+        </is>
+      </c>
+      <c r="H22" s="4" t="inlineStr">
+        <is>
+          <t>AC-32, AC-33</t>
+        </is>
+      </c>
+      <c r="I22" s="4" t="inlineStr">
+        <is>
+          <t>EM26-19 review log › CR-2026-08; review record CR-2026-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
           <t>2026-06</t>
         </is>
       </c>
-      <c r="B16" s="4" t="inlineStr">
+      <c r="B23" s="4" t="inlineStr">
         <is>
           <t>Client D (Gulf region)</t>
         </is>
       </c>
-      <c r="C16" s="4" t="inlineStr">
-        <is>
-          <t>Client ↔ AJACE</t>
-        </is>
-      </c>
-      <c r="D16" s="4" t="inlineStr">
-        <is>
-          <t>Document creation: PPT and PDF made locally, with and without a template, with images</t>
-        </is>
-      </c>
-      <c r="E16" s="4" t="inlineStr">
-        <is>
-          <t>Demonstration / meeting</t>
-        </is>
-      </c>
-      <c r="F16" s="4" t="inlineStr">
-        <is>
-          <t>Review record CR-2026-09; correspondence to be filed</t>
-        </is>
-      </c>
-      <c r="G16" s="4" t="inlineStr">
-        <is>
-          <t>2026</t>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>Requirements meeting</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>Document Studio (requirement and mediator contract)</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>PPT and PDF made locally, with and without a template, with images</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>Delivered from the existing build</t>
+        </is>
+      </c>
+      <c r="G23" s="4" t="inlineStr">
+        <is>
+          <t>FR-DS-01 … 04</t>
+        </is>
+      </c>
+      <c r="H23" s="4" t="inlineStr">
+        <is>
+          <t>AC-34</t>
+        </is>
+      </c>
+      <c r="I23" s="4" t="inlineStr">
+        <is>
+          <t>EM26-19 review log › CR-2026-09; review record CR-2026-09; EM26-28 CON-2026-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>Client E (Asia-Pacific)</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>Meetings</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>EchoMind IoT</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>Agritech sensor data and communication; vehicle inspection system</t>
+        </is>
+      </c>
+      <c r="F24" s="4" t="inlineStr">
+        <is>
+          <t>Requirements and contract in evaluation</t>
+        </is>
+      </c>
+      <c r="G24" s="4" t="inlineStr">
+        <is>
+          <t>New — to be defined</t>
+        </is>
+      </c>
+      <c r="H24" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I24" s="4" t="inlineStr">
+        <is>
+          <t>EM26-28 CON-2026-04</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:G16"/>
+  <autoFilter ref="A4:I24"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1046,7 +1554,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.1</t>
         </is>
       </c>
     </row>
@@ -1058,7 +1566,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
@@ -1070,7 +1578,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>APPROVED — 2026-10-13 (AR-2026-005)</t>
+          <t>Rev 1.1 issued for approval; rev 1.0 approved 2026-10-13 (AR-2026-005)</t>
         </is>
       </c>
     </row>
@@ -1106,7 +1614,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>Richard Watson Stephen Amudha (Lead Engineer) — 2026-10-13</t>
+          <t>Richard Watson Stephen Amudha (Lead Engineer) — 2026-10-14</t>
         </is>
       </c>
     </row>
@@ -1118,7 +1626,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Alexander Peter (EchoMind Project Lead) — 2026-10-13</t>
+          <t>Alexander Peter (EchoMind Project Lead) — rev 1.1 to confirm</t>
         </is>
       </c>
     </row>
@@ -1130,7 +1638,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Sheryl Nazareth (QA / MR) — 2026-10-13</t>
+          <t>Sheryl Nazareth (QA / MR) — rev 1.1 to confirm</t>
         </is>
       </c>
     </row>
@@ -1142,7 +1650,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Anita Johan (Managing Director) — 2026-10-13</t>
+          <t>Anita Johan (Managing Director) — rev 1.1 to confirm</t>
         </is>
       </c>
     </row>

--- a/docs/EchoMind_Audit_2026-10-14_Project2/03_Communication_with_Client/EM26-27_Client_Communication_Log.xlsx
+++ b/docs/EchoMind_Audit_2026-10-14_Project2/03_Communication_with_Client/EM26-27_Client_Communication_Log.xlsx
@@ -1578,7 +1578,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Rev 1.1 issued for approval; rev 1.0 approved 2026-10-13 (AR-2026-005)</t>
+          <t>APPROVED — rev 1.1 2026-10-20 (AR-2026-007); rev 1.0 approved 2026-10-13 (AR-2026-005)</t>
         </is>
       </c>
     </row>
@@ -1626,7 +1626,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Alexander Peter (EchoMind Project Lead) — rev 1.1 to confirm</t>
+          <t>Alexander Peter (EchoMind Project Lead) — 2026-10-20</t>
         </is>
       </c>
     </row>
@@ -1638,7 +1638,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Sheryl Nazareth (QA / MR) — rev 1.1 to confirm</t>
+          <t>Sheryl Nazareth (QA / MR) — 2026-10-20</t>
         </is>
       </c>
     </row>
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Anita Johan (Managing Director) — rev 1.1 to confirm</t>
+          <t>Anita Johan (Managing Director) — 2026-10-20</t>
         </is>
       </c>
     </row>
